--- a/OMM12_genome_statistics.xlsx
+++ b/OMM12_genome_statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Members\!Monica Steffi Matchado\OMM12_review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E007871B-31D1-468F-ADF1-F7BF3BB59B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4CC91C-B88E-4A81-9650-B4B294F082D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{ABF51BCC-B901-4528-81EA-B0146D425A63}"/>
   </bookViews>
@@ -985,7 +985,7 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="25.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="72.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1083,7 +1083,7 @@
       <c r="G5" s="26"/>
       <c r="H5" s="23"/>
     </row>
-    <row r="6" spans="1:8" ht="58" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="72.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="H10" s="9"/>
     </row>
-    <row r="11" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14"/>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -1312,14 +1312,14 @@
         <v>37</v>
       </c>
       <c r="F16" s="24">
+        <v>39</v>
+      </c>
+      <c r="G16" s="24">
         <v>1</v>
       </c>
-      <c r="G16" s="24">
-        <v>39</v>
-      </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -1348,14 +1348,14 @@
         <v>40</v>
       </c>
       <c r="F18" s="24">
+        <v>50</v>
+      </c>
+      <c r="G18" s="24">
         <v>1</v>
       </c>
-      <c r="G18" s="24">
-        <v>50</v>
-      </c>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -1384,14 +1384,14 @@
         <v>43</v>
       </c>
       <c r="F20" s="24">
+        <v>44</v>
+      </c>
+      <c r="G20" s="24">
         <v>0</v>
       </c>
-      <c r="G20" s="24">
-        <v>44</v>
-      </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
